--- a/artfynd/A 38588-2021 artfynd.xlsx
+++ b/artfynd/A 38588-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38588-2021 artfynd.xlsx
+++ b/artfynd/A 38588-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56145398</v>
+        <v>104023536</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stordalsberget, Ång</t>
+          <t>Dalabäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550576.4665052971</v>
+        <v>550473</v>
       </c>
       <c r="R2" t="n">
-        <v>7088906.633903552</v>
+        <v>7088925</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-05-21</t>
+          <t>2022-06-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-05-21</t>
+          <t>2022-06-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,48 +766,30 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>bäckskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gran</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niina Sallmén, Ulrika Westling</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104023537</v>
+        <v>56145398</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnberget, Ång</t>
+          <t>Stordalsberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550345.3182028361</v>
+        <v>550576</v>
       </c>
       <c r="R3" t="n">
-        <v>7088921.828687114</v>
+        <v>7088907</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:43</t>
+          <t>2015-05-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:43</t>
+          <t>2015-05-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,57 +867,65 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>bäckskog</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gran</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Niina Sallmén, Ulrika Westling</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104023538</v>
+        <v>104023537</v>
       </c>
       <c r="B4" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -960,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550322.0208870957</v>
+        <v>550345</v>
       </c>
       <c r="R4" t="n">
-        <v>7088945.658130848</v>
+        <v>7088922</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +970,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +980,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,50 +1011,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104023536</v>
+        <v>104023540</v>
       </c>
       <c r="B5" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dalabäcken, Ång</t>
+          <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550473.0461347466</v>
+        <v>550252</v>
       </c>
       <c r="R5" t="n">
-        <v>7088925.647329924</v>
+        <v>7088942</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,6 +1102,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1145,6 +1120,233 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104023538</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>550322</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7088945</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bodum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-06-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-06-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104023535</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dalabäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>550488</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7088933</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bodum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-06-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-06-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
